--- a/frontend/e2e/fixtures/assignments_import.xlsx
+++ b/frontend/e2e/fixtures/assignments_import.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>班級</t>
+          <t>班级</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -429,27 +429,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>教師</t>
+          <t>教师</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>每週節數</t>
+          <t>每周节数</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>連堂長度</t>
+          <t>连堂长度</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>連堂次數</t>
+          <t>连堂次数</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>場地類型</t>
+          <t>场地类型</t>
         </is>
       </c>
     </row>
@@ -493,37 +493,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>範例</t>
+          <t>示例</t>
         </is>
       </c>
     </row>
@@ -535,12 +535,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>機械實習</t>
+          <t>机械实习</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>陳師、林師</t>
+          <t>陈师、林师</t>
         </is>
       </c>
       <c r="D4" t="n">
